--- a/USHPRR/UMo_defect_relaxation_volume.xlsx
+++ b/USHPRR/UMo_defect_relaxation_volume.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/spreadsheets/USHPRR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D84DAC9-FF14-6545-A34A-F8C05728F1EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2984FC-D943-C649-9968-459591CDC9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1300" yWindow="6160" windowWidth="35560" windowHeight="17420" activeTab="2" xr2:uid="{E6C385B5-DE39-C74D-9E54-74BB84BFBA62}"/>
+    <workbookView xWindow="9220" yWindow="7520" windowWidth="35560" windowHeight="17420" activeTab="2" xr2:uid="{E6C385B5-DE39-C74D-9E54-74BB84BFBA62}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -248,18 +248,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -843,6 +841,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -850,7 +849,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1700,6 +1698,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1707,7 +1706,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2478,6 +2476,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2485,7 +2484,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3335,6 +3333,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3342,7 +3341,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3702,6 +3700,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3709,7 +3708,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4311,6 +4309,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4318,7 +4317,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5216,6 +5214,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5223,7 +5222,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6071,6 +6069,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6078,7 +6077,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6680,6 +6678,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6687,7 +6686,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -12377,48 +12375,48 @@
     </row>
     <row r="2" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5"/>
+      <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4">
         <v>0.84518796504250548</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5">
         <v>0.71434269625269153</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6">
         <v>0.61912359500358871</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7">
         <v>5.735481409893281E-2</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>5</v>
       </c>
     </row>
@@ -12428,156 +12426,154 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4" t="s">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
+      <c r="A12" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12">
         <v>2.4678700283107469E-2</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12">
         <v>2.4678700283107469E-2</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12">
         <v>7.5020945050079657</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12">
         <v>7.1398596972900907E-2</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
+      <c r="A13" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13">
         <v>3</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13">
         <v>9.8687241009694261E-3</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13">
         <v>3.2895747003231419E-3</v>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="2">
         <v>4</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="2">
         <v>3.4547424384076895E-2</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
     </row>
     <row r="15" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4" t="s">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+      <c r="A17" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17">
         <v>2.6311069970837302</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17">
         <v>2.5649852632415423E-2</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17">
         <v>102.57786018460884</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17">
         <v>2.0424962770474888E-6</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17">
         <v>2.549477718342628</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17">
         <v>2.7127362758248323</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17">
         <v>2.549477718342628</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17">
         <v>2.7127362758248323</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="2">
         <v>-15.916722667856989</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="2">
         <v>5.8111539883944259</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="2">
         <v>-2.7389951633779797</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="2">
         <v>7.1398596972900907E-2</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <v>-34.410408207657518</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="2">
         <v>2.5769628719435413</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="2">
         <v>-34.410408207657518</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="2">
         <v>2.5769628719435413</v>
       </c>
     </row>
@@ -15467,21 +15463,21 @@
       <c r="S6">
         <v>-2.0823076657564341</v>
       </c>
-      <c r="V6" s="6">
+      <c r="V6">
         <v>0</v>
       </c>
-      <c r="W6" s="6" cm="1">
+      <c r="W6" cm="1">
         <f t="array" ref="W6:X6">LINEST(B6:B10,A6:A10)</f>
         <v>9.8563562641549116E-3</v>
       </c>
-      <c r="X6" s="6">
+      <c r="X6">
         <v>3.8008243045852388</v>
       </c>
-      <c r="Y6" s="6" cm="1">
+      <c r="Y6" cm="1">
         <f t="array" ref="Y6:Z6">LINEST(L$6:L$10,$A$6:$A$10)</f>
         <v>-3.6543100395607903E-2</v>
       </c>
-      <c r="Z6" s="6">
+      <c r="Z6">
         <v>-2.5320259672183929</v>
       </c>
     </row>
@@ -15540,21 +15536,21 @@
       <c r="S7">
         <v>-2.1064387055167906</v>
       </c>
-      <c r="V7" s="6">
+      <c r="V7">
         <v>0.12</v>
       </c>
-      <c r="W7" s="6" cm="1">
+      <c r="W7" cm="1">
         <f t="array" ref="W7:X7">LINEST(C$6:C$10,$A$6:$A$10)</f>
         <v>2.1936239464750651E-2</v>
       </c>
-      <c r="X7" s="6">
+      <c r="X7">
         <v>4.7444936177981116</v>
       </c>
-      <c r="Y7" s="6" cm="1">
+      <c r="Y7" cm="1">
         <f t="array" ref="Y7:Z7">LINEST(M$6:M$10,$A$6:$A$10)</f>
         <v>-1.3199895075402975E-2</v>
       </c>
-      <c r="Z7" s="6">
+      <c r="Z7">
         <v>-2.4603790288435001</v>
       </c>
     </row>
@@ -15613,21 +15609,21 @@
       <c r="S8">
         <v>-2.1542082563185816</v>
       </c>
-      <c r="V8" s="6">
+      <c r="V8">
         <v>0.22</v>
       </c>
-      <c r="W8" s="6" cm="1">
+      <c r="W8" cm="1">
         <f t="array" ref="W8:X8">LINEST(D$6:D$10,$A$6:$A$10)</f>
         <v>2.0045389601622558E-2</v>
       </c>
-      <c r="X8" s="6">
+      <c r="X8">
         <v>5.5432039222290159</v>
       </c>
-      <c r="Y8" s="6" cm="1">
+      <c r="Y8" cm="1">
         <f t="array" ref="Y8:Z8">LINEST(N$6:N$10,$A$6:$A$10)</f>
         <v>-1.1133961749623507E-2</v>
       </c>
-      <c r="Z8" s="6">
+      <c r="Z8">
         <v>-2.3734175318894217</v>
       </c>
     </row>
@@ -15686,21 +15682,21 @@
       <c r="S9">
         <v>-1.9573986700422883</v>
       </c>
-      <c r="V9" s="6">
+      <c r="V9">
         <v>0.3</v>
       </c>
-      <c r="W9" s="6" cm="1">
+      <c r="W9" cm="1">
         <f t="array" ref="W9:X9">LINEST(E$6:E$10,$A$6:$A$10)</f>
         <v>2.3011979780358266E-2</v>
       </c>
-      <c r="X9" s="6">
+      <c r="X9">
         <v>6.2107339837926876</v>
       </c>
-      <c r="Y9" s="6" cm="1">
+      <c r="Y9" cm="1">
         <f t="array" ref="Y9:Z9">LINEST(O$6:O$10,$A$6:$A$10)</f>
         <v>-1.1275924870714951E-2</v>
       </c>
-      <c r="Z9" s="6">
+      <c r="Z9">
         <v>-2.3618537795914767</v>
       </c>
     </row>
@@ -15759,40 +15755,40 @@
       <c r="S10">
         <v>-2.029017596818731</v>
       </c>
-      <c r="V10" s="6">
+      <c r="V10">
         <v>0.52</v>
       </c>
-      <c r="W10" s="6" cm="1">
+      <c r="W10" cm="1">
         <f t="array" ref="W10:X10">LINEST(F$6:F$10,$A$6:$A$10)</f>
         <v>2.3775801176341246E-2</v>
       </c>
-      <c r="X10" s="6">
+      <c r="X10">
         <v>8.496963391822689</v>
       </c>
-      <c r="Y10" s="6" cm="1">
+      <c r="Y10" cm="1">
         <f t="array" ref="Y10:Z10">LINEST(P$6:P$10,$A$6:$A$10)</f>
         <v>-1.6731271189927868E-2</v>
       </c>
-      <c r="Z10" s="6">
+      <c r="Z10">
         <v>-2.5775445181094807</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="V11" s="6">
+      <c r="V11">
         <v>0.71</v>
       </c>
-      <c r="W11" s="6" cm="1">
+      <c r="W11" cm="1">
         <f t="array" ref="W11:X11">LINEST(G$6:G$10,$A$6:$A$10)</f>
         <v>1.1806877587229536E-2</v>
       </c>
-      <c r="X11" s="6">
+      <c r="X11">
         <v>10.325692875753598</v>
       </c>
-      <c r="Y11" s="6" cm="1">
+      <c r="Y11" cm="1">
         <f t="array" ref="Y11:Z11">LINEST(Q$6:Q$10,$A$6:$A$10)</f>
         <v>-1.3867757281166038E-2</v>
       </c>
-      <c r="Z11" s="6">
+      <c r="Z11">
         <v>-2.7762000807547813</v>
       </c>
     </row>
@@ -15803,21 +15799,21 @@
       <c r="L12" t="s">
         <v>5</v>
       </c>
-      <c r="V12" s="6">
+      <c r="V12">
         <v>0.85</v>
       </c>
-      <c r="W12" s="6" cm="1">
+      <c r="W12" cm="1">
         <f t="array" ref="W12:X12">LINEST(H$6:H$10,$A$6:$A$10)</f>
         <v>1.2662546551493072E-2</v>
       </c>
-      <c r="X12" s="6">
+      <c r="X12">
         <v>11.319652803667498</v>
       </c>
-      <c r="Y12" s="6" cm="1">
+      <c r="Y12" cm="1">
         <f t="array" ref="Y12:Z12">LINEST(R$6:R$10,$A$6:$A$10)</f>
         <v>-1.1449158051551564E-2</v>
       </c>
-      <c r="Z12" s="6">
+      <c r="Z12">
         <v>-2.612677211023668</v>
       </c>
     </row>
@@ -15876,21 +15872,21 @@
       <c r="S13">
         <v>1</v>
       </c>
-      <c r="V13" s="6">
+      <c r="V13">
         <v>1</v>
       </c>
-      <c r="W13" s="6" cm="1">
+      <c r="W13" cm="1">
         <f t="array" ref="W13:X13">LINEST(I$6:I$10,$A$6:$A$10)</f>
         <v>1.2065226187725995E-2</v>
       </c>
-      <c r="X13" s="6">
+      <c r="X13">
         <v>13.029222632776589</v>
       </c>
-      <c r="Y13" s="6" cm="1">
+      <c r="Y13" cm="1">
         <f t="array" ref="Y13:Z13">LINEST(S$6:S$10,$A$6:$A$10)</f>
         <v>-7.9884270894840757E-3</v>
       </c>
-      <c r="Z13" s="6">
+      <c r="Z13">
         <v>-2.065874178890565</v>
       </c>
     </row>
@@ -15949,11 +15945,6 @@
       <c r="S14">
         <v>-2.0675007514945074</v>
       </c>
-      <c r="V14" s="6"/>
-      <c r="W14" s="6"/>
-      <c r="X14" s="6"/>
-      <c r="Y14" s="6"/>
-      <c r="Z14" s="6"/>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A15">
@@ -16010,17 +16001,14 @@
       <c r="S15">
         <v>-2.1343414754721781</v>
       </c>
-      <c r="V15" s="6"/>
-      <c r="W15" s="6">
+      <c r="W15">
         <f>AVERAGE(W6:W13)</f>
         <v>1.6895052076709528E-2</v>
       </c>
-      <c r="X15" s="6"/>
-      <c r="Y15" s="6">
+      <c r="Y15">
         <f>AVERAGE(Y6:Y13)</f>
         <v>-1.5273686962934864E-2</v>
       </c>
-      <c r="Z15" s="6"/>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A16">
@@ -16077,11 +16065,6 @@
       <c r="S16">
         <v>-2.2048206662493843</v>
       </c>
-      <c r="V16" s="6"/>
-      <c r="W16" s="6"/>
-      <c r="X16" s="6"/>
-      <c r="Y16" s="6"/>
-      <c r="Z16" s="6"/>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A17">
@@ -16138,17 +16121,15 @@
       <c r="S17">
         <v>-2.0097577796647075</v>
       </c>
-      <c r="V17" s="6">
+      <c r="V17">
         <v>600</v>
       </c>
-      <c r="W17" s="6" t="s">
+      <c r="W17" t="s">
         <v>34</v>
       </c>
-      <c r="X17" s="6"/>
-      <c r="Y17" s="6" t="s">
+      <c r="Y17" t="s">
         <v>35</v>
       </c>
-      <c r="Z17" s="6"/>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A18">
@@ -16205,28 +16186,23 @@
       <c r="S18">
         <v>-2.0039307589565438</v>
       </c>
-      <c r="V18" s="6"/>
-      <c r="W18" s="6"/>
-      <c r="X18" s="6"/>
-      <c r="Y18" s="6"/>
-      <c r="Z18" s="6"/>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="V19" s="6">
+      <c r="V19">
         <v>0</v>
       </c>
-      <c r="W19" s="6" cm="1">
+      <c r="W19" cm="1">
         <f t="array" ref="W19:X19">LINEST(B$30:B$34,$A$30:$A$34)</f>
         <v>-7.8572240902262201E-3</v>
       </c>
-      <c r="X19" s="6">
+      <c r="X19">
         <v>2.6089102798354666</v>
       </c>
-      <c r="Y19" s="6" cm="1">
+      <c r="Y19" cm="1">
         <f t="array" ref="Y19:Z19">LINEST(L$30:L$34,$A$30:$A$34)</f>
         <v>-7.2278931023643564E-2</v>
       </c>
-      <c r="Z19" s="6">
+      <c r="Z19">
         <v>-2.2476834515602588</v>
       </c>
     </row>
@@ -16237,21 +16213,21 @@
       <c r="L20" t="s">
         <v>6</v>
       </c>
-      <c r="V20" s="6">
+      <c r="V20">
         <v>0.12</v>
       </c>
-      <c r="W20" s="6" cm="1">
+      <c r="W20" cm="1">
         <f t="array" ref="W20:X20">LINEST(C$30:C$34,$A$30:$A$34)</f>
         <v>2.4569576191792133E-2</v>
       </c>
-      <c r="X20" s="6">
+      <c r="X20">
         <v>3.3748630070965149</v>
       </c>
-      <c r="Y20" s="6" cm="1">
+      <c r="Y20" cm="1">
         <f t="array" ref="Y20:Z20">LINEST(M$30:M$34,$A$30:$A$34)</f>
         <v>-1.4027458621788098E-2</v>
       </c>
-      <c r="Z20" s="6">
+      <c r="Z20">
         <v>-2.9743679182844853</v>
       </c>
     </row>
@@ -16310,21 +16286,21 @@
       <c r="S21">
         <v>1</v>
       </c>
-      <c r="V21" s="6">
+      <c r="V21">
         <v>0.22</v>
       </c>
-      <c r="W21" s="6" cm="1">
+      <c r="W21" cm="1">
         <f t="array" ref="W21:X21">LINEST(D$30:D$34,$A$30:$A$34)</f>
         <v>2.9644143651536229E-2</v>
       </c>
-      <c r="X21" s="6">
+      <c r="X21">
         <v>4.6627270093351196</v>
       </c>
-      <c r="Y21" s="6" cm="1">
+      <c r="Y21" cm="1">
         <f t="array" ref="Y21:Z21">LINEST(N$30:N$34,$A$30:$A$34)</f>
         <v>-6.9103618031381682E-3</v>
       </c>
-      <c r="Z21" s="6">
+      <c r="Z21">
         <v>-2.5312686150193846</v>
       </c>
     </row>
@@ -16383,21 +16359,21 @@
       <c r="S22">
         <v>-2.0921482833895646</v>
       </c>
-      <c r="V22" s="6">
+      <c r="V22">
         <v>0.3</v>
       </c>
-      <c r="W22" s="6" cm="1">
+      <c r="W22" cm="1">
         <f t="array" ref="W22:X22">LINEST(E$30:E$34,$A$30:$A$34)</f>
         <v>3.1052040418446725E-2</v>
       </c>
-      <c r="X22" s="6">
+      <c r="X22">
         <v>5.9405391973176505</v>
       </c>
-      <c r="Y22" s="6" cm="1">
+      <c r="Y22" cm="1">
         <f t="array" ref="Y22:Z22">LINEST(O$30:O$34,$A$30:$A$34)</f>
         <v>-9.835233814286231E-3</v>
       </c>
-      <c r="Z22" s="6">
+      <c r="Z22">
         <v>-2.3824652163505369</v>
       </c>
     </row>
@@ -16456,21 +16432,21 @@
       <c r="S23">
         <v>-2.1635988709355982</v>
       </c>
-      <c r="V23" s="6">
+      <c r="V23">
         <v>0.52</v>
       </c>
-      <c r="W23" s="6" cm="1">
+      <c r="W23" cm="1">
         <f t="array" ref="W23:X23">LINEST(F$30:F$34,$A$30:$A$34)</f>
         <v>2.6181204504806561E-2</v>
       </c>
-      <c r="X23" s="6">
+      <c r="X23">
         <v>9.80145322635558</v>
       </c>
-      <c r="Y23" s="6" cm="1">
+      <c r="Y23" cm="1">
         <f t="array" ref="Y23:Z23">LINEST(P$30:P$34,$A$30:$A$34)</f>
         <v>-1.642480504670514E-2</v>
       </c>
-      <c r="Z23" s="6">
+      <c r="Z23">
         <v>-2.6609001387694158</v>
       </c>
     </row>
@@ -16529,21 +16505,21 @@
       <c r="S24">
         <v>-2.2511494830333501</v>
       </c>
-      <c r="V24" s="6">
+      <c r="V24">
         <v>0.71</v>
       </c>
-      <c r="W24" s="6" cm="1">
+      <c r="W24" cm="1">
         <f t="array" ref="W24:X24">LINEST(G$30:G$34,$A$30:$A$34)</f>
         <v>7.7570817037625178E-3</v>
       </c>
-      <c r="X24" s="6">
+      <c r="X24">
         <v>11.711308191935512</v>
       </c>
-      <c r="Y24" s="6" cm="1">
+      <c r="Y24" cm="1">
         <f t="array" ref="Y24:Z24">LINEST(Q$30:Q$34,$A$30:$A$34)</f>
         <v>-1.0948395289141327E-2</v>
       </c>
-      <c r="Z24" s="6">
+      <c r="Z24">
         <v>-2.9572423890184059</v>
       </c>
     </row>
@@ -16602,21 +16578,21 @@
       <c r="S25">
         <v>-2.0516465627052902</v>
       </c>
-      <c r="V25" s="6">
+      <c r="V25">
         <v>0.85</v>
       </c>
-      <c r="W25" s="6" cm="1">
+      <c r="W25" cm="1">
         <f t="array" ref="W25:X25">LINEST(H$30:H$34,$A$30:$A$34)</f>
         <v>1.0011490898758349E-2</v>
       </c>
-      <c r="X25" s="6">
+      <c r="X25">
         <v>12.383179143223806</v>
       </c>
-      <c r="Y25" s="6" cm="1">
+      <c r="Y25" cm="1">
         <f t="array" ref="Y25:Z25">LINEST(R$30:R$34,$A$30:$A$34)</f>
         <v>-8.7636336012856825E-3</v>
       </c>
-      <c r="Z25" s="6">
+      <c r="Z25">
         <v>-2.7668802749216708</v>
       </c>
     </row>
@@ -16675,21 +16651,21 @@
       <c r="S26">
         <v>-2.0211393231300403</v>
       </c>
-      <c r="V26" s="6">
+      <c r="V26">
         <v>1</v>
       </c>
-      <c r="W26" s="6" cm="1">
+      <c r="W26" cm="1">
         <f t="array" ref="W26:X26">LINEST(I$30:I$34,$A$30:$A$34)</f>
         <v>1.0423468893522846E-2</v>
       </c>
-      <c r="X26" s="6">
+      <c r="X26">
         <v>13.958746343622053</v>
       </c>
-      <c r="Y26" s="6" cm="1">
+      <c r="Y26" cm="1">
         <f t="array" ref="Y26:Z26">LINEST(S$30:S$34,$A$30:$A$34)</f>
         <v>-6.6293593756430172E-3</v>
       </c>
-      <c r="Z26" s="6">
+      <c r="Z26">
         <v>-2.1043832148392863</v>
       </c>
     </row>

--- a/USHPRR/UMo_defect_relaxation_volume.xlsx
+++ b/USHPRR/UMo_defect_relaxation_volume.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/spreadsheets/USHPRR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2984FC-D943-C649-9968-459591CDC9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED7AF07-C720-4F4A-998C-D8E243A79661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9220" yWindow="7520" windowWidth="35560" windowHeight="17420" activeTab="2" xr2:uid="{E6C385B5-DE39-C74D-9E54-74BB84BFBA62}"/>
   </bookViews>
